--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/SVZ-CHILE_Datenbank/after_conversion_chile_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/SVZ-CHILE_Datenbank/after_conversion_chile_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="59">
   <si>
     <t>location</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Database_number</t>
+  </si>
+  <si>
+    <t>Database_name</t>
   </si>
   <si>
     <t>Nevado de Chillan Vn.</t>
@@ -551,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD31"/>
+  <dimension ref="A1:AE31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.7109375" customWidth="1"/>
@@ -577,9 +580,10 @@
     <col min="28" max="28" width="18.7109375" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" customWidth="1"/>
     <col min="30" max="30" width="17.7109375" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -670,13 +674,16 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C2">
         <v>-36.86333</v>
@@ -721,12 +728,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3">
         <v>-36.86333</v>
@@ -768,12 +775,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4">
         <v>-36.86333</v>
@@ -815,12 +822,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C5">
         <v>-37.82667</v>
@@ -865,12 +872,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:31">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>-37.85</v>
@@ -912,12 +919,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>-37.85</v>
@@ -959,12 +966,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8">
         <v>-37.85</v>
@@ -1006,12 +1013,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:31">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9">
         <v>-37.85</v>
@@ -1056,12 +1063,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:31">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C10">
         <v>-37.99123</v>
@@ -1106,12 +1113,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11">
         <v>-38.06739</v>
@@ -1156,12 +1163,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:31">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C12">
         <v>-38.47289</v>
@@ -1203,12 +1210,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13">
         <v>-38.18931</v>
@@ -1253,12 +1260,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14">
         <v>-38.23439</v>
@@ -1303,12 +1310,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:31">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15">
         <v>-38.31</v>
@@ -1350,12 +1357,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:31">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16">
         <v>-38.5833</v>
@@ -1399,10 +1406,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C17">
         <v>-38.58015</v>
@@ -1449,10 +1456,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C18">
         <v>-38.95637</v>
@@ -1499,10 +1506,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C19">
         <v>-39.14</v>
@@ -1549,10 +1556,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C20">
         <v>-39.21944</v>
@@ -1599,10 +1606,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C21">
         <v>-39.32877</v>
@@ -1649,10 +1656,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22">
         <v>-39.34004</v>
@@ -1699,10 +1706,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C23">
         <v>-39.42105</v>
@@ -1749,10 +1756,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C24">
         <v>-39.42062</v>
@@ -1799,10 +1806,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C25">
         <v>-39.6</v>
@@ -1849,10 +1856,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C26">
         <v>-39.635</v>
@@ -1899,10 +1906,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C27">
         <v>-39.74</v>
@@ -1949,10 +1956,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C28">
         <v>-40.19396</v>
@@ -1999,10 +2006,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C29">
         <v>-40.71223</v>
@@ -2049,10 +2056,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C30">
         <v>-40.73555</v>
@@ -2099,10 +2106,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C31">
         <v>-40.85889</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/SVZ-CHILE_Datenbank/after_conversion_chile_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/SVZ-CHILE_Datenbank/after_conversion_chile_mapped_readable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="60">
   <si>
     <t>location</t>
   </si>
@@ -191,6 +191,9 @@
   </si>
   <si>
     <t>LOFS</t>
+  </si>
+  <si>
+    <t>Andesite</t>
   </si>
 </sst>
 </file>
@@ -691,6 +694,9 @@
       <c r="D2">
         <v>-71.37667</v>
       </c>
+      <c r="F2" t="s">
+        <v>59</v>
+      </c>
       <c r="H2">
         <v>68</v>
       </c>
@@ -741,6 +747,9 @@
       <c r="D3">
         <v>-71.37667</v>
       </c>
+      <c r="F3" t="s">
+        <v>59</v>
+      </c>
       <c r="H3">
         <v>82</v>
       </c>
@@ -788,6 +797,9 @@
       <c r="D4">
         <v>-71.37667</v>
       </c>
+      <c r="F4" t="s">
+        <v>59</v>
+      </c>
       <c r="H4">
         <v>91</v>
       </c>
@@ -835,6 +847,9 @@
       <c r="D5">
         <v>-71.13</v>
       </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
       <c r="H5">
         <v>45</v>
       </c>
@@ -885,6 +900,9 @@
       <c r="D6">
         <v>-71.17</v>
       </c>
+      <c r="F6" t="s">
+        <v>59</v>
+      </c>
       <c r="H6">
         <v>87</v>
       </c>
@@ -932,6 +950,9 @@
       <c r="D7">
         <v>-71.17</v>
       </c>
+      <c r="F7" t="s">
+        <v>59</v>
+      </c>
       <c r="H7">
         <v>93</v>
       </c>
@@ -979,6 +1000,9 @@
       <c r="D8">
         <v>-71.17</v>
       </c>
+      <c r="F8" t="s">
+        <v>59</v>
+      </c>
       <c r="H8">
         <v>88</v>
       </c>
@@ -1026,6 +1050,9 @@
       <c r="D9">
         <v>-71.17</v>
       </c>
+      <c r="F9" t="s">
+        <v>59</v>
+      </c>
       <c r="H9">
         <v>47</v>
       </c>
@@ -1076,6 +1103,9 @@
       <c r="D10">
         <v>-71.53136000000001</v>
       </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
       <c r="H10">
         <v>78</v>
       </c>
@@ -1126,6 +1156,9 @@
       <c r="D11">
         <v>-71.71277000000001</v>
       </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
       <c r="H11">
         <v>38.5</v>
       </c>
@@ -1176,6 +1209,9 @@
       <c r="D12">
         <v>-71.36324</v>
       </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
       <c r="H12">
         <v>82</v>
       </c>
@@ -1223,6 +1259,9 @@
       <c r="D13">
         <v>-71.0365</v>
       </c>
+      <c r="F13" t="s">
+        <v>59</v>
+      </c>
       <c r="H13">
         <v>36</v>
       </c>
@@ -1273,6 +1312,9 @@
       <c r="D14">
         <v>-71.72808999999999</v>
       </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
       <c r="H14">
         <v>85.5</v>
       </c>
@@ -1323,6 +1365,9 @@
       <c r="D15">
         <v>-71.645</v>
       </c>
+      <c r="F15" t="s">
+        <v>59</v>
+      </c>
       <c r="H15">
         <v>92</v>
       </c>
@@ -1370,6 +1415,9 @@
       <c r="D16">
         <v>-71.58329999999999</v>
       </c>
+      <c r="F16" t="s">
+        <v>59</v>
+      </c>
       <c r="H16">
         <v>87</v>
       </c>
@@ -1417,6 +1465,9 @@
       <c r="D17">
         <v>-71.62808</v>
       </c>
+      <c r="F17" t="s">
+        <v>59</v>
+      </c>
       <c r="H17">
         <v>35</v>
       </c>
@@ -1467,6 +1518,9 @@
       <c r="D18">
         <v>-71.70944</v>
       </c>
+      <c r="F18" t="s">
+        <v>59</v>
+      </c>
       <c r="H18">
         <v>45</v>
       </c>
@@ -1517,6 +1571,9 @@
       <c r="D19">
         <v>-71.48999999999999</v>
       </c>
+      <c r="F19" t="s">
+        <v>59</v>
+      </c>
       <c r="H19">
         <v>51</v>
       </c>
@@ -1567,6 +1624,9 @@
       <c r="D20">
         <v>-71.69588</v>
       </c>
+      <c r="F20" t="s">
+        <v>59</v>
+      </c>
       <c r="H20">
         <v>45</v>
       </c>
@@ -1617,6 +1677,9 @@
       <c r="D21">
         <v>-71.72086</v>
       </c>
+      <c r="F21" t="s">
+        <v>59</v>
+      </c>
       <c r="H21">
         <v>42</v>
       </c>
@@ -1667,6 +1730,9 @@
       <c r="D22">
         <v>-71.69108</v>
       </c>
+      <c r="F22" t="s">
+        <v>59</v>
+      </c>
       <c r="H22">
         <v>40</v>
       </c>
@@ -1717,6 +1783,9 @@
       <c r="D23">
         <v>-71.78619</v>
       </c>
+      <c r="F23" t="s">
+        <v>59</v>
+      </c>
       <c r="H23">
         <v>50</v>
       </c>
@@ -1767,6 +1836,9 @@
       <c r="D24">
         <v>-71.67094</v>
       </c>
+      <c r="F24" t="s">
+        <v>59</v>
+      </c>
       <c r="H24">
         <v>37</v>
       </c>
@@ -1817,6 +1889,9 @@
       <c r="D25">
         <v>-71.95</v>
       </c>
+      <c r="F25" t="s">
+        <v>59</v>
+      </c>
       <c r="H25">
         <v>50</v>
       </c>
@@ -1867,6 +1942,9 @@
       <c r="D26">
         <v>-71.9233</v>
       </c>
+      <c r="F26" t="s">
+        <v>59</v>
+      </c>
       <c r="H26">
         <v>74.59999999999999</v>
       </c>
@@ -1917,6 +1995,9 @@
       <c r="D27">
         <v>-71.84999999999999</v>
       </c>
+      <c r="F27" t="s">
+        <v>59</v>
+      </c>
       <c r="H27">
         <v>37.2</v>
       </c>
@@ -1967,6 +2048,9 @@
       <c r="D28">
         <v>-71.9345</v>
       </c>
+      <c r="F28" t="s">
+        <v>59</v>
+      </c>
       <c r="H28">
         <v>82.5</v>
       </c>
@@ -2017,6 +2101,9 @@
       <c r="D29">
         <v>-72.32695</v>
       </c>
+      <c r="F29" t="s">
+        <v>59</v>
+      </c>
       <c r="H29">
         <v>60</v>
       </c>
@@ -2067,6 +2154,9 @@
       <c r="D30">
         <v>-72.30749</v>
       </c>
+      <c r="F30" t="s">
+        <v>59</v>
+      </c>
       <c r="H30">
         <v>66</v>
       </c>
@@ -2116,6 +2206,9 @@
       </c>
       <c r="D31">
         <v>-72.22278</v>
+      </c>
+      <c r="F31" t="s">
+        <v>59</v>
       </c>
       <c r="H31">
         <v>80</v>

--- a/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/SVZ-CHILE_Datenbank/after_conversion_chile_mapped_readable.xlsx
+++ b/Abschlussarbeit Bearbeitung/Jupyter Notebooks/1.1_Data-Acquisition-Wrapper/Zwischenstände/SVZ-CHILE_Datenbank/after_conversion_chile_mapped_readable.xlsx
@@ -807,13 +807,16 @@
         <v>2.4</v>
       </c>
       <c r="L4">
-        <v>16.63112752551153</v>
+        <v>18.52061952917278</v>
       </c>
       <c r="N4">
-        <v>1.157036419113215</v>
+        <v>2.527211125957812</v>
+      </c>
+      <c r="O4">
+        <v>2.139477473770829</v>
       </c>
       <c r="P4">
-        <v>1.297469933629422</v>
+        <v>2.028544338539847</v>
       </c>
       <c r="Q4">
         <v>0.3334273624823695</v>
@@ -822,10 +825,10 @@
         <v>9.179575265459087</v>
       </c>
       <c r="S4">
-        <v>0.9521967720365538</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>2.079374295046076</v>
+        <v>0.6803364852180274</v>
       </c>
       <c r="V4">
         <v>1632.047477744807</v>
@@ -910,13 +913,16 @@
         <v>2.7</v>
       </c>
       <c r="L6">
-        <v>27.5523865636992</v>
+        <v>28.31882445972851</v>
       </c>
       <c r="N6">
-        <v>0.543720121763729</v>
+        <v>0.9960952630711514</v>
+      </c>
+      <c r="O6">
+        <v>0.9956799012548858</v>
       </c>
       <c r="P6">
-        <v>0.6038225460352312</v>
+        <v>0.8857727431508557</v>
       </c>
       <c r="Q6">
         <v>0.0062059238363892</v>
@@ -925,10 +931,10 @@
         <v>23.50614199458672</v>
       </c>
       <c r="S6">
-        <v>0.3753064729713783</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>0.9079678656105252</v>
+        <v>0.3197069949332835</v>
       </c>
       <c r="V6">
         <v>1609.221638895229</v>
@@ -960,13 +966,16 @@
         <v>3.6</v>
       </c>
       <c r="L7">
-        <v>6.907230042490595</v>
+        <v>7.461714377447538</v>
       </c>
       <c r="N7">
-        <v>0.5393703607896191</v>
+        <v>1.204883789828423</v>
+      </c>
+      <c r="O7">
+        <v>0.0987451141740382</v>
       </c>
       <c r="P7">
-        <v>0.0598832277059733</v>
+        <v>0.5214831079395179</v>
       </c>
       <c r="Q7">
         <v>0.0090267983074753</v>
@@ -975,10 +984,10 @@
         <v>4.315219654382677</v>
       </c>
       <c r="S7">
-        <v>0.4539733319348114</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>0.53455009552845</v>
+        <v>0.3171493389738172</v>
       </c>
       <c r="V7">
         <v>995.2065738415886</v>
